--- a/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris est dans le jardin avec maman. C'est un après-midi ensoleillé. Ava est là aussi. Ava a un peu de gâteau sur la joue. Iris voit le téléphone de maman. Iris a une idée de photo. Maman tient le téléphone. Iris dit : je peux prendre une photo ? Maman dit : on doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Maman dit : le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. Iris dit : d'accord. Elle demande encore. Maman dit oui, pour un souvenir. Ava essuie sa joue. Maman prend la photo. Iris et Ava sourient. Le téléphone reste dans la main de maman. Iris dit merci. Les abeilles butinent près des fleurs. Papa arrive plus tard. Maman montre la photo. Iris a demandé.</t>
+          <t>Iris est dans le jardin avec maman. C'est un après-midi ensoleillé. Ava est là aussi. Ava a un peu de gâteau sur la joue. Iris voit le téléphone de maman. Iris a une idée de photo. Maman tient le téléphone. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. D'accord. Elle demande encore. Maman dit oui, pour un souvenir. Ava essuie sa joue. Maman prend la photo. Iris et Ava sourient. Le téléphone reste dans la main de maman. Iris dit merci. Les abeilles butinent près des fleurs. Papa arrive plus tard. Maman montre la photo. Iris a demandé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Iris est dans le jardin avec maman. C'est un après-midi ensoleillé. Ava est là aussi. Ava a un peu de gâteau sur la joue. Iris voit le téléphone de maman. Iris a une idée de photo. Maman tient le téléphone.
+enfant-f|Je peux prendre une photo ?
+maman|On doit demander. Demander, c'est parler avant.
+narrateur|Une photo se fait avec un adulte.
+maman|Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre.
+enfant-f|D'accord. Elle demande encore. Maman dit oui, pour un souvenir.
+narrateur|Ava essuie sa joue. Maman prend la photo. Iris et Ava sourient. Le téléphone reste dans la main de maman. Iris dit merci. Les abeilles butinent près des fleurs. Papa arrive plus tard. Maman montre la photo. Iris a demandé.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Iris veut une photo. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Iris a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Iris et Ava rangent les assiettes. Maman glisse le téléphone dans sa poche.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Ava essuie sa joue. Maman prend la photo. Iris et Ava sourient. Le téléphone reste dans la main de maman. Iris dit merci. Les abeilles butinent près des fleurs. Papa arrive plus tard. Maman montre la photo. Iris a demandé.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Iris veut une photo. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Iris a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Iris et Ava rangent les assiettes. Maman glisse le téléphone dans sa poche.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La photo d'Iris avec maman</t>
+          <t>Le souvenir des lavandes</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les abeilles vont près des lavandes. Nina veut un souvenir. Elle demande. Maman garde le téléphone. Victorina sourit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris est dans le jardin avec maman. C'est un après-midi ensoleillé. Ava est là aussi. Ava a un peu de gâteau sur la joue. Iris voit le téléphone de maman. Iris a une idée de photo. Maman tient le téléphone. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. D'accord. Elle demande encore. Maman dit oui, pour un souvenir. Ava essuie sa joue. Maman prend la photo. Iris et Ava sourient. Le téléphone reste dans la main de maman. Iris dit merci. Les abeilles butinent près des fleurs. Papa arrive plus tard. Maman montre la photo. Iris a demandé.</t>
+          <t>Les abeilles vont et viennent près des lavandes. Le muret de pierre est chaud sous la main. Les verres de limonade transpirent un peu. Une nappe à petits carreaux sent le soleil. Il reste une assiette de gâteau, toute ronde. Une fourchette a un peu de crème au bout. La pierre du muret tient encore le soleil. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Maman le tient déjà dans la main. Nina a une idée de souvenir. Maman. Je peux demander une photo ? Oui. On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. On sourit ensemble. Ce n'est pas pour rire de l'autre. D'accord. Je demande encore. Tu peux prendre une photo, maman ? Oui, pour un souvenir. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Maman prend la photo. Nina et Victorina sourient. Le téléphone reste dans la main de maman. Merci, maman. Bravo, Nina. Tu as demandé. C'est du bon travail. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. Nina a demandé une photo. Le téléphone est resté avec moi. Bravo, Nina. Une photo, c'est un souvenir. On demande à l'adulte. J'ai demandé. On a souri. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Nina a demandé. Le téléphone reste dans ma poche, après. Une photo, c'est avec un adulte. J'ai parlé avant. Oui. Tu as demandé. Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Iris est dans le jardin avec maman. C'est un après-midi ensoleillé. Ava est là aussi. Ava a un peu de gâteau sur la joue. Iris voit le téléphone de maman. Iris a une idée de photo. Maman tient le téléphone.
-enfant-f|Je peux prendre une photo ?
-maman|On doit demander. Demander, c'est parler avant.
-narrateur|Une photo se fait avec un adulte.
-maman|Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre.
-enfant-f|D'accord. Elle demande encore. Maman dit oui, pour un souvenir.
-narrateur|Ava essuie sa joue. Maman prend la photo. Iris et Ava sourient. Le téléphone reste dans la main de maman. Iris dit merci. Les abeilles butinent près des fleurs. Papa arrive plus tard. Maman montre la photo. Iris a demandé.</t>
+          <t>narrateur|Les abeilles vont et viennent près des lavandes.
+narrateur|Le muret de pierre est chaud sous la main.
+narrateur|Les verres de limonade transpirent un peu.
+narrateur|Une nappe à petits carreaux sent le soleil.
+narrateur|Il reste une assiette de gâteau, toute ronde.
+narrateur|Une fourchette a un peu de crème au bout.
+narrateur|La pierre du muret tient encore le soleil.
+maman|Le jardin sent bon, Nina.
+maman|Victorina est là aussi.
+enfant-f|Les abeilles font un bruit tout fin.
+maman|Oui.
+maman|On les regarde, sans les toucher.
+narrateur|En ce moment, Nina et Victorina sont près du muret.
+narrateur|Victorina a un peu de gâteau sur la joue.
+narrateur|Nina voit le téléphone de maman.
+narrateur|Maman le tient déjà dans la main.
+narrateur|Nina a une idée de souvenir.
+enfant-f|Maman.
+enfant-f|Je peux demander une photo ?
+maman|Oui.
+maman|On doit demander.
+maman|Demander, c'est parler avant.
+maman|Une photo se fait avec un adulte.
+maman|Le téléphone reste avec l'adulte.
+maman|Une photo, c'est un souvenir.
+maman|On sourit ensemble.
+maman|Ce n'est pas pour rire de l'autre.
+enfant-f|D'accord.
+enfant-f|Je demande encore.
+enfant-f|Tu peux prendre une photo, maman ?
+maman|Oui, pour un souvenir.
+maman|Victorina, tu veux essuyer ta joue ?
+narrateur|Victorina essuie sa joue.
+narrateur|Le gâteau n'est plus là.
+maman|Vous souriez toutes les deux ?
+enfant-f|Oui, maman.
+narrateur|Maman prend la photo.
+narrateur|Nina et Victorina sourient.
+narrateur|Le téléphone reste dans la main de maman.
+enfant-f|Merci, maman.
+maman|Bravo, Nina.
+maman|Tu as demandé.
+maman|C'est du bon travail.
+narrateur|Les abeilles butinent encore près des fleurs.
+narrateur|Papa arrive plus tard, par le petit portail.
+papa|Je vous trouve au jardin.
+papa|Ça sent la lavande.
+maman|Nina a demandé une photo.
+maman|Le téléphone est resté avec moi.
+papa|Bravo, Nina.
+papa|Une photo, c'est un souvenir.
+papa|On demande à l'adulte.
+enfant-f|J'ai demandé.
+enfant-f|On a souri.
+papa|Vous me montrez ?
+maman|Oui.
+narrateur|Maman montre la photo.
+narrateur|Le téléphone reste avec elle.
+narrateur|Nina a demandé.
+maman|Le téléphone reste dans ma poche, après.
+papa|Une photo, c'est avec un adulte.
+enfant-f|J'ai parlé avant.
+maman|Oui.
+maman|Tu as demandé.
+narrateur|Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Iris veut une photo. Que fait-elle ?</t>
+          <t>Nina veut une photo. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Iris veut une photo. Que fait-elle ?</t>
+          <t>narrateur|Nina veut une photo.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Iris a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Maman est là.</t>
+          <t>Nina a su demander. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. Ce n'est pas pour rire de l'autre. Bravo. C'est du bon travail, Nina. J'ai demandé. À maman. Oui. On demande à l'adulte. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1745,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Iris a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Maman est là.</t>
+          <t>narrateur|Nina a su demander.
+narrateur|Le téléphone reste avec l'adulte.
+narrateur|Une photo, c'est un souvenir.
+maman|Ce n'est pas pour rire de l'autre.
+maman|Bravo.
+maman|C'est du bon travail, Nina.
+enfant-f|J'ai demandé.
+enfant-f|À maman.
+papa|Oui.
+papa|On demande à l'adulte.
+narrateur|Les abeilles s'éloignent un peu.
+narrateur|Le muret reste chaud.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Iris et Ava rangent les assiettes. Maman glisse le téléphone dans sa poche.</t>
+          <t>Nina et Victorina rangent les assiettes. La nappe a un peu de sucre. Merci, les filles. Maman glisse le téléphone dans sa poche. Les verres sont encore un peu froids. On a un souvenir, maintenant. Oui. Parce que tu as demandé. On reste encore un peu au jardin ? Oui, papa. La lavande sent toujours fort. Le portail reste entrouvert.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1920,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Iris et Ava rangent les assiettes. Maman glisse le téléphone dans sa poche.</t>
+          <t>narrateur|Nina et Victorina rangent les assiettes.
+narrateur|La nappe a un peu de sucre.
+maman|Merci, les filles.
+narrateur|Maman glisse le téléphone dans sa poche.
+papa|Les verres sont encore un peu froids.
+enfant-f|On a un souvenir, maintenant.
+maman|Oui.
+maman|Parce que tu as demandé.
+papa|On reste encore un peu au jardin ?
+enfant-f|Oui, papa.
+narrateur|La lavande sent toujours fort.
+narrateur|Le portail reste entrouvert.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai demandé. Maman a gardé le téléphone. Bravo. Tu as fait du bon travail. C'est un souvenir. Les abeilles ont fini leur ronde. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2099,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai demandé.
+enfant-f|Maman a gardé le téléphone.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|C'est un souvenir.
+narrateur|Les abeilles ont fini leur ronde.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les abeilles vont et viennent près des lavandes. Le muret de pierre est chaud sous la main. Les verres de limonade transpirent un peu. Une nappe à petits carreaux sent le soleil. Il reste une assiette de gâteau, toute ronde. Une fourchette a un peu de crème au bout. La pierre du muret tient encore le soleil. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Maman le tient déjà dans la main. Nina a une idée de souvenir. Maman. Je peux demander une photo ? Oui. On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. On sourit ensemble. Ce n'est pas pour rire de l'autre. D'accord. Je demande encore. Tu peux prendre une photo, maman ? Oui, pour un souvenir. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Maman prend la photo. Nina et Victorina sourient. Le téléphone reste dans la main de maman. Merci, maman. Bravo, Nina. Tu as demandé. C'est du bon travail. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. Nina a demandé une photo. Le téléphone est resté avec moi. Bravo, Nina. Une photo, c'est un souvenir. On demande à l'adulte. J'ai demandé. On a souri. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Nina a demandé. Le téléphone reste dans ma poche, après. Une photo, c'est avec un adulte. J'ai parlé avant. Oui. Tu as demandé. Un verre de limonade laisse un rond d'eau.</t>
+          <t>Les abeilles vont et viennent près des lavandes. Le muret de pierre est chaud sous la main. Les verres de limonade transpirent un peu. Une nappe à petits carreaux sent le soleil. Il reste une assiette de gâteau, toute ronde. Une fourchette a un peu de crème au bout. La pierre du muret tient encore le soleil. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Maman le tient déjà dans la main. Nina a une idée de souvenir. Maman. Je peux demander une photo ? Oui. On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. On sourit ensemble. Ce n'est pas pour rire de l'autre. D'accord. Je demande encore. Tu peux prendre une photo, maman ? Oui, pour un souvenir. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Maman prend la photo. Nina et Victorina sourient. Le téléphone reste dans la main de maman. Merci, maman. Bravo, Nina. Tu as demandé. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. Nina a demandé une photo. Le téléphone est resté avec moi. Bravo, Nina. Une photo, c'est un souvenir. On demande à l'adulte. J'ai demandé. On a souri. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Nina a demandé. Le téléphone reste dans ma poche, après. Une photo, c'est avec un adulte. J'ai parlé avant. Oui. Tu as demandé. Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris est dans le jardin avec maman. C'est un après-midi ensoleillé. Ava est là aussi. Ava a un peu de gâteau sur la joue. Iris voit le téléphone de maman. Iris a une idée de photo. Maman tient le téléphone. Iris dit : je peux prendre une photo ? Maman dit : on doit &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Demander, c'est parler avant. Une photo se fait avec un adulte. Maman dit : le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. Iris dit : d'accord. Elle demande encore. Maman dit oui, pour un souvenir. Ava essuie sa joue. Maman prend la photo. Iris et Ava sourient. Le téléphone reste dans la main de maman. Iris dit merci. Les abeilles butinent près des fleurs. Papa arrive plus tard. Maman montre la photo. Iris a demandé.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les abeilles vont et viennent près des lavandes. Le muret de pierre est chaud sous la main. Les verres de limonade transpirent un peu. Une nappe à petits carreaux sent le soleil. Il reste une assiette de gâteau, toute ronde. Une fourchette a un peu de crème au bout. La pierre du muret tient encore le soleil. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Maman le tient déjà dans la main. Nina a une idée de souvenir. Maman. Je peux demander une photo ? Oui. On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. On sourit ensemble. Ce n'est pas pour rire de l'autre. D'accord. Je demande encore. Tu peux prendre une photo, maman ? Oui, pour un souvenir. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Maman prend la photo. Nina et Victorina sourient. Le téléphone reste dans la main de maman. Merci, maman. Bravo, Nina. Tu as demandé. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. Nina a demandé une photo. Le téléphone est resté avec moi. Bravo, Nina. Une photo, c'est un souvenir. On demande à l'adulte. J'ai demandé. On a souri. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Nina a demandé. Le téléphone reste dans ma poche, après. Une photo, c'est avec un adulte. J'ai parlé avant. Oui. Tu as demandé. Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 enfant-f|Merci, maman.
 maman|Bravo, Nina.
 maman|Tu as demandé.
-maman|C'est du bon travail.
 narrateur|Les abeilles butinent encore près des fleurs.
 narrateur|Papa arrive plus tard, par le petit portail.
 papa|Je vous trouve au jardin.
@@ -1391,7 +1390,6 @@
 narrateur|Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1421,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris veut une photo. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina veut une photo. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1574,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su demander. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. Ce n'est pas pour rire de l'autre. Bravo. C'est du bon travail, Nina. J'ai demandé. À maman. Oui. On demande à l'adulte. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
+          <t>Nina a su demander. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. Ce n'est pas pour rire de l'autre. Bravo. J'ai demandé. À maman. Oui. On demande à l'adulte. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris a su &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a su demander. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. Ce n'est pas pour rire de l'autre. Bravo. J'ai demandé. À maman. Oui. On demande à l'adulte. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,7 +1747,6 @@
 narrateur|Une photo, c'est un souvenir.
 maman|Ce n'est pas pour rire de l'autre.
 maman|Bravo.
-maman|C'est du bon travail, Nina.
 enfant-f|J'ai demandé.
 enfant-f|À maman.
 papa|Oui.
@@ -1759,7 +1755,6 @@
 narrateur|Le muret reste chaud.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris et Ava rangent les assiettes. Maman glisse le téléphone dans sa poche.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina et Victorina rangent les assiettes. La nappe a un peu de sucre. Merci, les filles. Maman glisse le téléphone dans sa poche. Les verres sont encore un peu froids. On a un souvenir, maintenant. Oui. Parce que tu as demandé. On reste encore un peu au jardin ? Oui, papa. La lavande sent toujours fort. Le portail reste entrouvert.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,7 +1929,6 @@
 narrateur|Le portail reste entrouvert.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1959,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé. Maman a gardé le téléphone. Bravo. Tu as fait du bon travail. C'est un souvenir. Les abeilles ont fini leur ronde. L'histoire est finie.</t>
+          <t>J'ai demandé. Maman a gardé le téléphone. Bravo. C'est un souvenir. Les abeilles ont fini leur ronde.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai demandé. Maman a gardé le téléphone. Bravo. C'est un souvenir. Les abeilles ont fini leur ronde.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,13 +2096,10 @@
           <t>enfant-f|J'ai demandé.
 enfant-f|Maman a gardé le téléphone.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 papa|C'est un souvenir.
-narrateur|Les abeilles ont fini leur ronde.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les abeilles ont fini leur ronde.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2163,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iris, Ava, maman</t>
+          <t>Nina, Victorina, maman, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-01.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le souvenir des lavandes</t>
+          <t>La lavande du muret</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, muret, lavande, gâteau</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Les abeilles vont près des lavandes. Nina veut un souvenir. Elle demande. Maman garde le téléphone. Victorina sourit.</t>
+          <t>Nina veut un souvenir près des lavandes. Victorina a du gâteau sur la joue. Nina avance la main vers le téléphone. Maman attend. Nina parle. Alors la photo. Plus tard, les abeilles. Papa attend. Nina parle encore.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les abeilles vont et viennent près des lavandes. Le muret de pierre est chaud sous la main. Les verres de limonade transpirent un peu. Une nappe à petits carreaux sent le soleil. Il reste une assiette de gâteau, toute ronde. Une fourchette a un peu de crème au bout. La pierre du muret tient encore le soleil. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Maman le tient déjà dans la main. Nina a une idée de souvenir. Maman. Je peux demander une photo ? Oui. On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. On sourit ensemble. Ce n'est pas pour rire de l'autre. D'accord. Je demande encore. Tu peux prendre une photo, maman ? Oui, pour un souvenir. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Maman prend la photo. Nina et Victorina sourient. Le téléphone reste dans la main de maman. Merci, maman. Bravo, Nina. Tu as demandé. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. Nina a demandé une photo. Le téléphone est resté avec moi. Bravo, Nina. Une photo, c'est un souvenir. On demande à l'adulte. J'ai demandé. On a souri. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Nina a demandé. Le téléphone reste dans ma poche, après. Une photo, c'est avec un adulte. J'ai parlé avant. Oui. Tu as demandé. Un verre de limonade laisse un rond d'eau.</t>
+          <t>La lavande du jardin sent le savon chaud. Les abeilles font un bruit tout fin. Le muret de pierre tient encore le soleil. Une miette sucrée brille près d'une assiette. Une fourchette a un peu de crème au bout. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Il est sur la nappe, près du verre. Je veux un souvenir, près des fleurs. Nina avance la main vers le téléphone. Maman ne bouge pas. Maman attend, tout près. Nina pose sa main. Maman, je peux demander une photo ? Oui. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Oui. Maman lève le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Nina et Victorina sont près des lavandes. Merci, maman. Bravo, Nina. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. On a un souvenir. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Une abeille tourne près du muret. Encore une, papa. Avec l'abeille. Nina avance encore la main. Papa ne bouge pas. Papa attend. Papa, tu peux ? Oui. Papa lève le téléphone. Le téléphone reste dans sa main. La photo se fait, près de la fleur. Merci, papa. De rien. Le téléphone rentre dans ma poche, après. On a souri. Oui. Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Les abeilles vont et viennent près des lavandes. Le muret de pierre est chaud sous la main. Les verres de limonade transpirent un peu. Une nappe à petits carreaux sent le soleil. Il reste une assiette de gâteau, toute ronde. Une fourchette a un peu de crème au bout. La pierre du muret tient encore le soleil. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Maman le tient déjà dans la main. Nina a une idée de souvenir. Maman. Je peux demander une photo ? Oui. On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. On sourit ensemble. Ce n'est pas pour rire de l'autre. D'accord. Je demande encore. Tu peux prendre une photo, maman ? Oui, pour un souvenir. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Maman prend la photo. Nina et Victorina sourient. Le téléphone reste dans la main de maman. Merci, maman. Bravo, Nina. Tu as demandé. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. Nina a demandé une photo. Le téléphone est resté avec moi. Bravo, Nina. Une photo, c'est un souvenir. On demande à l'adulte. J'ai demandé. On a souri. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Nina a demandé. Le téléphone reste dans ma poche, après. Une photo, c'est avec un adulte. J'ai parlé avant. Oui. Tu as demandé. Un verre de limonade laisse un rond d'eau.</t>
+          <t>La lavande du jardin sent le savon chaud. Les abeilles font un bruit tout fin. Le muret de pierre tient encore le soleil. Une miette sucrée brille près d'une assiette. Une fourchette a un peu de crème au bout. Le jardin sent bon, Nina. Victorina est là aussi. Les abeilles font un bruit tout fin. Oui. On les regarde, sans les toucher. En ce moment, Nina et Victorina sont près du muret. Victorina a un peu de gâteau sur la joue. Nina voit le téléphone de maman. Il est sur la nappe, près du verre. Je veux un souvenir, près des fleurs. Nina avance la main vers le téléphone. Maman ne bouge pas. Maman attend, tout près. Nina pose sa main. Maman, je peux demander une photo ? Oui. Victorina, tu veux essuyer ta joue ? Victorina essuie sa joue. Le gâteau n'est plus là. Vous souriez toutes les deux ? Oui, maman. Oui. Maman lève le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Nina et Victorina sont près des lavandes. Merci, maman. Bravo, Nina. Les abeilles butinent encore près des fleurs. Papa arrive plus tard, par le petit portail. Je vous trouve au jardin. Ça sent la lavande. On a un souvenir. Vous me montrez ? Oui. Maman montre la photo. Le téléphone reste avec elle. Une abeille tourne près du muret. Encore une, papa. Avec l'abeille. Nina avance encore la main. Papa ne bouge pas. Papa attend. Papa, tu peux ? Oui. Papa lève le téléphone. Le téléphone reste dans sa main. La photo se fait, près de la fleur. Merci, papa. De rien. Le téléphone rentre dans ma poche, après. On a souri. Oui. Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,13 +1324,11 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les abeilles vont et viennent près des lavandes.
-narrateur|Le muret de pierre est chaud sous la main.
-narrateur|Les verres de limonade transpirent un peu.
-narrateur|Une nappe à petits carreaux sent le soleil.
-narrateur|Il reste une assiette de gâteau, toute ronde.
+          <t>narrateur|La lavande du jardin sent le savon chaud.
+narrateur|Les abeilles font un bruit tout fin.
+narrateur|Le muret de pierre tient encore le soleil.
+narrateur|Une miette sucrée brille près d'une assiette.
 narrateur|Une fourchette a un peu de crème au bout.
-narrateur|La pierre du muret tient encore le soleil.
 maman|Le jardin sent bon, Nina.
 maman|Victorina est là aussi.
 enfant-f|Les abeilles font un bruit tout fin.
@@ -1339,54 +1337,51 @@
 narrateur|En ce moment, Nina et Victorina sont près du muret.
 narrateur|Victorina a un peu de gâteau sur la joue.
 narrateur|Nina voit le téléphone de maman.
-narrateur|Maman le tient déjà dans la main.
-narrateur|Nina a une idée de souvenir.
-enfant-f|Maman.
-enfant-f|Je peux demander une photo ?
+narrateur|Il est sur la nappe, près du verre.
+enfant-f|Je veux un souvenir, près des fleurs.
+narrateur|Nina avance la main vers le téléphone.
+narrateur|Maman ne bouge pas.
+narrateur|Maman attend, tout près.
+narrateur|Nina pose sa main.
+enfant-f|Maman, je peux demander une photo ?
 maman|Oui.
-maman|On doit demander.
-maman|Demander, c'est parler avant.
-maman|Une photo se fait avec un adulte.
-maman|Le téléphone reste avec l'adulte.
-maman|Une photo, c'est un souvenir.
-maman|On sourit ensemble.
-maman|Ce n'est pas pour rire de l'autre.
-enfant-f|D'accord.
-enfant-f|Je demande encore.
-enfant-f|Tu peux prendre une photo, maman ?
-maman|Oui, pour un souvenir.
 maman|Victorina, tu veux essuyer ta joue ?
 narrateur|Victorina essuie sa joue.
 narrateur|Le gâteau n'est plus là.
 maman|Vous souriez toutes les deux ?
 enfant-f|Oui, maman.
+copine|Oui.
+narrateur|Maman lève le téléphone.
+narrateur|Le téléphone reste dans sa main.
 narrateur|Maman prend la photo.
-narrateur|Nina et Victorina sourient.
-narrateur|Le téléphone reste dans la main de maman.
+narrateur|Nina et Victorina sont près des lavandes.
 enfant-f|Merci, maman.
 maman|Bravo, Nina.
-maman|Tu as demandé.
 narrateur|Les abeilles butinent encore près des fleurs.
 narrateur|Papa arrive plus tard, par le petit portail.
 papa|Je vous trouve au jardin.
 papa|Ça sent la lavande.
-maman|Nina a demandé une photo.
-maman|Le téléphone est resté avec moi.
-papa|Bravo, Nina.
-papa|Une photo, c'est un souvenir.
-papa|On demande à l'adulte.
-enfant-f|J'ai demandé.
-enfant-f|On a souri.
+enfant-f|On a un souvenir.
 papa|Vous me montrez ?
 maman|Oui.
 narrateur|Maman montre la photo.
 narrateur|Le téléphone reste avec elle.
-narrateur|Nina a demandé.
-maman|Le téléphone reste dans ma poche, après.
-papa|Une photo, c'est avec un adulte.
-enfant-f|J'ai parlé avant.
-maman|Oui.
-maman|Tu as demandé.
+narrateur|Une abeille tourne près du muret.
+enfant-f|Encore une, papa.
+enfant-f|Avec l'abeille.
+narrateur|Nina avance encore la main.
+narrateur|Papa ne bouge pas.
+narrateur|Papa attend.
+enfant-f|Papa, tu peux ?
+papa|Oui.
+narrateur|Papa lève le téléphone.
+narrateur|Le téléphone reste dans sa main.
+narrateur|La photo se fait, près de la fleur.
+enfant-f|Merci, papa.
+papa|De rien.
+maman|Le téléphone rentre dans ma poche, après.
+enfant-f|On a souri.
+papa|Oui.
 narrateur|Un verre de limonade laisse un rond d'eau.</t>
         </is>
       </c>
@@ -1434,7 +1429,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | à maman | adulte | demander à l'adulte</t>
+          <t>demander | à maman | adulte | demander à l'adulte | je peux</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1449,7 +1444,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On demande à l'adulte. Ce n'est pas pour rire de l'autre. Que fait Iris ?</t>
+          <t>Nina parle à maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1491,14 +1486,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1598,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su demander. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. Ce n'est pas pour rire de l'autre. Bravo. J'ai demandé. À maman. Oui. On demande à l'adulte. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
+          <t>Nina a parlé à maman. Puis à papa. Alors les photos sont arrivées. Bravo. J'ai parlé avant. À maman. Oui. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nina a su demander. Le téléphone reste avec l'adulte. Une photo, c'est un souvenir. Ce n'est pas pour rire de l'autre. Bravo. J'ai demandé. À maman. Oui. On demande à l'adulte. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
+          <t>Nina a parlé à maman. Puis à papa. Alors les photos sont arrivées. Bravo. J'ai parlé avant. À maman. Oui. Les abeilles s'éloignent un peu. Le muret reste chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1666,7 +1661,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1742,15 +1737,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a su demander.
-narrateur|Le téléphone reste avec l'adulte.
-narrateur|Une photo, c'est un souvenir.
-maman|Ce n'est pas pour rire de l'autre.
+          <t>narrateur|Nina a parlé à maman.
+narrateur|Puis à papa.
+narrateur|Alors les photos sont arrivées.
 maman|Bravo.
-enfant-f|J'ai demandé.
+enfant-f|J'ai parlé avant.
 enfant-f|À maman.
 papa|Oui.
-papa|On demande à l'adulte.
 narrateur|Les abeilles s'éloignent un peu.
 narrateur|Le muret reste chaud.</t>
         </is>
@@ -1779,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina et Victorina rangent les assiettes. La nappe a un peu de sucre. Merci, les filles. Maman glisse le téléphone dans sa poche. Les verres sont encore un peu froids. On a un souvenir, maintenant. Oui. Parce que tu as demandé. On reste encore un peu au jardin ? Oui, papa. La lavande sent toujours fort. Le portail reste entrouvert.</t>
+          <t>Nina et Victorina rangent les assiettes. La nappe a un peu de sucre. Merci, les filles. Maman glisse le téléphone dans sa poche. Les verres sont encore un peu froids. On a un souvenir, maintenant. Oui. On reste encore un peu au jardin ? Oui, papa. La lavande sent toujours fort. Le portail reste entrouvert.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nina et Victorina rangent les assiettes. La nappe a un peu de sucre. Merci, les filles. Maman glisse le téléphone dans sa poche. Les verres sont encore un peu froids. On a un souvenir, maintenant. Oui. Parce que tu as demandé. On reste encore un peu au jardin ? Oui, papa. La lavande sent toujours fort. Le portail reste entrouvert.</t>
+          <t>Nina et Victorina rangent les assiettes. La nappe a un peu de sucre. Merci, les filles. Maman glisse le téléphone dans sa poche. Les verres sont encore un peu froids. On a un souvenir, maintenant. Oui. On reste encore un peu au jardin ? Oui, papa. La lavande sent toujours fort. Le portail reste entrouvert.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1847,7 +1840,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1915,6 @@
 papa|Les verres sont encore un peu froids.
 enfant-f|On a un souvenir, maintenant.
 maman|Oui.
-maman|Parce que tu as demandé.
 papa|On reste encore un peu au jardin ?
 enfant-f|Oui, papa.
 narrateur|La lavande sent toujours fort.
@@ -1953,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé. Maman a gardé le téléphone. Bravo. C'est un souvenir. Les abeilles ont fini leur ronde.</t>
+          <t>On a un souvenir. Près des fleurs. Bravo. C'est pour nous. Les abeilles ont fini leur ronde.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé. Maman a gardé le téléphone. Bravo. C'est un souvenir. Les abeilles ont fini leur ronde.</t>
+          <t>On a un souvenir. Près des fleurs. Bravo. C'est pour nous. Les abeilles ont fini leur ronde.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2021,7 +2013,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2093,10 +2085,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai demandé.
-enfant-f|Maman a gardé le téléphone.
+          <t>enfant-f|On a un souvenir.
+enfant-f|Près des fleurs.
 maman|Bravo.
-papa|C'est un souvenir.
+papa|C'est pour nous.
 narrateur|Les abeilles ont fini leur ronde.</t>
         </is>
       </c>
@@ -2118,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2160,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
